--- a/informes_data/Primera FEB/2025-26/playoffs/individual/NP_play_by_play_2513251_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/playoffs/individual/NP_play_by_play_2513251_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.783899999999999</v>
+        <v>9.7308</v>
       </c>
       <c r="E2" t="n">
-        <v>9.59</v>
+        <v>9.536899999999999</v>
       </c>
       <c r="F2" t="n">
         <v>0.1939</v>
@@ -610,10 +610,10 @@
         <v>2.2027</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2765</v>
+        <v>0.2234</v>
       </c>
       <c r="T2" t="n">
-        <v>0.353</v>
+        <v>0.2999</v>
       </c>
       <c r="U2" t="n">
         <v>-0.0765</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1695</v>
+        <v>4.2944</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5168</v>
+        <v>3.6994</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6526999999999999</v>
+        <v>0.5951</v>
       </c>
       <c r="G3" t="n">
         <v>1.4687</v>
@@ -688,13 +688,13 @@
         <v>1.7622</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2509</v>
+        <v>0.8741</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4562</v>
+        <v>0.7262999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2054</v>
+        <v>0.1477</v>
       </c>
       <c r="V3" t="n">
         <v>0.1895</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. NIANG</t>
+          <t>L. NWOGBO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7934</v>
+        <v>2.1954</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7478</v>
+        <v>1.9206</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0456</v>
+        <v>0.2748</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0846</v>
+        <v>-1.2508</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7378</v>
+        <v>-0.6442</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6532</v>
+        <v>-0.6066</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2105</v>
+        <v>-0.1281</v>
       </c>
       <c r="K4" t="n">
-        <v>2.0586</v>
+        <v>-0.3939</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1519</v>
+        <v>0.2658</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1259</v>
+        <v>-1.1227</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3208</v>
+        <v>-0.2503</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8051</v>
+        <v>-0.8724</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2203</v>
+        <v>1.3216</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1014</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>1.3216</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6735</v>
+        <v>0.4507</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6386</v>
+        <v>0.3749</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0349</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.185</v>
+        <v>1.6739</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.6739</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. STUMBRIS</t>
+          <t>M. NIANG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5471</v>
+        <v>1.8318</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2232</v>
+        <v>1.7574</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3239</v>
+        <v>0.0745</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4087</v>
+        <v>1.0846</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.3589</v>
+        <v>1.7378</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9503</v>
+        <v>-0.6532</v>
       </c>
       <c r="J5" t="n">
-        <v>0.897</v>
+        <v>2.2105</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.546</v>
+        <v>2.0586</v>
       </c>
       <c r="L5" t="n">
-        <v>1.443</v>
+        <v>0.1519</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3056</v>
+        <v>-1.1259</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8129999999999999</v>
+        <v>-0.3208</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4927</v>
+        <v>-0.8051</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3216</v>
+        <v>0.2203</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1014</v>
       </c>
       <c r="R5" t="n">
         <v>1.3216</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6341</v>
+        <v>0.712</v>
       </c>
       <c r="T5" t="n">
-        <v>1.3262</v>
+        <v>0.6482</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3079</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.185</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.185</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. NWOGBO</t>
+          <t>L. GIOVANNETTI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.308</v>
+        <v>1.5302</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0909</v>
+        <v>0.2793</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2171</v>
+        <v>1.2509</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.2508</v>
+        <v>0.2426</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6442</v>
+        <v>-0.2088</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6066</v>
+        <v>0.4513</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1281</v>
+        <v>0.7215</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3939</v>
+        <v>0.9166</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2658</v>
+        <v>-0.1952</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1227</v>
+        <v>-0.4789</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2503</v>
+        <v>-1.1254</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8724</v>
+        <v>0.6465</v>
       </c>
       <c r="P6" t="n">
         <v>1.3216</v>
@@ -922,19 +922,19 @@
         <v>1.3216</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5633</v>
+        <v>-0.034</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5451</v>
+        <v>-0.4422</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0182</v>
+        <v>0.4082</v>
       </c>
       <c r="V6" t="n">
-        <v>1.6739</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.6739</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. GIOVANNETTI</t>
+          <t>R. STUMBRIS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3247</v>
+        <v>1.4387</v>
       </c>
       <c r="E7" t="n">
-        <v>0.045</v>
+        <v>1.4031</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2798</v>
+        <v>0.0356</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2426</v>
+        <v>-0.4087</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2088</v>
+        <v>-1.3589</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4513</v>
+        <v>0.9503</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7215</v>
+        <v>0.897</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9166</v>
+        <v>-0.546</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1952</v>
+        <v>1.443</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4789</v>
+        <v>-1.3056</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1254</v>
+        <v>-0.8129999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6465</v>
+        <v>-0.4927</v>
       </c>
       <c r="P7" t="n">
         <v>1.3216</v>
@@ -1000,13 +1000,13 @@
         <v>1.3216</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2395</v>
+        <v>0.5256999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6765</v>
+        <v>0.5061</v>
       </c>
       <c r="U7" t="n">
-        <v>0.437</v>
+        <v>0.0196</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. GRANGER</t>
+          <t>T. MC GREW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0577</v>
+        <v>0.2584</v>
       </c>
       <c r="E8" t="n">
-        <v>1.067</v>
+        <v>0.2593</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1247</v>
+        <v>-0.0009</v>
       </c>
       <c r="G8" t="n">
-        <v>0.08459999999999999</v>
+        <v>-0.0185</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7119</v>
+        <v>-1.0438</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7965</v>
+        <v>1.0253</v>
       </c>
       <c r="J8" t="n">
-        <v>2.375</v>
+        <v>1.242</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5003</v>
+        <v>-0.8792</v>
       </c>
       <c r="L8" t="n">
-        <v>2.8754</v>
+        <v>2.1212</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.2905</v>
+        <v>-1.2605</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2116</v>
+        <v>-0.1646</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.0789</v>
+        <v>-1.0959</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.9825</v>
+        <v>0.8811</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.3041</v>
+        <v>-1.1014</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3216</v>
+        <v>1.9825</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0231</v>
+        <v>0.5147</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1327</v>
+        <v>0.1186</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1558</v>
+        <v>0.3961</v>
       </c>
       <c r="V8" t="n">
-        <v>1.8634</v>
+        <v>-1.1189</v>
       </c>
       <c r="W8" t="n">
-        <v>1.8634</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.1189</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. MC GREW</t>
+          <t>J. GRANGER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1617</v>
+        <v>0.2388</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1032</v>
+        <v>1.2482</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0585</v>
+        <v>-1.0094</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0185</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.0438</v>
+        <v>-0.7119</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0253</v>
+        <v>0.7965</v>
       </c>
       <c r="J9" t="n">
-        <v>1.242</v>
+        <v>2.375</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.8792</v>
+        <v>-0.5003</v>
       </c>
       <c r="L9" t="n">
-        <v>2.1212</v>
+        <v>2.8754</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2605</v>
+        <v>-2.2905</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1646</v>
+        <v>-0.2116</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0959</v>
+        <v>-2.0789</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8811</v>
+        <v>-1.9825</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1014</v>
+        <v>-3.3041</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9825</v>
+        <v>1.3216</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0946</v>
+        <v>0.2734</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2438</v>
+        <v>0.3139</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3384</v>
+        <v>-0.0405</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.1189</v>
+        <v>1.8634</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.8634</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2812</v>
+        <v>-0.4811</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4607</v>
+        <v>0.5778</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7419</v>
+        <v>-1.0589</v>
       </c>
       <c r="G10" t="n">
         <v>0.4634</v>
@@ -1234,13 +1234,13 @@
         <v>0.6608000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>0.273</v>
+        <v>0.073</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3203</v>
+        <v>-0.2031</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5931999999999999</v>
+        <v>0.2762</v>
       </c>
       <c r="V10" t="n">
         <v>-1.6784</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8292</v>
+        <v>-2.1785</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8295</v>
+        <v>-1.4671</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9997</v>
+        <v>-0.7114</v>
       </c>
       <c r="G11" t="n">
         <v>-3.4554</v>
@@ -1312,13 +1312,13 @@
         <v>1.5419</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3562</v>
+        <v>0.2945</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0765</v>
+        <v>0.4389</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4327</v>
+        <v>-0.1445</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5595</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.193</v>
+        <v>-3.8145</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.8763</v>
+        <v>-4.642</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6833</v>
+        <v>0.8274</v>
       </c>
       <c r="G12" t="n">
         <v>-3.9681</v>
@@ -1390,13 +1390,13 @@
         <v>1.7622</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7007</v>
+        <v>-0.3222</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8687</v>
+        <v>-0.6343</v>
       </c>
       <c r="U12" t="n">
-        <v>0.168</v>
+        <v>0.3121</v>
       </c>
       <c r="V12" t="n">
         <v>-0.185</v>
@@ -1423,28 +1423,28 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>14.4038</v>
+        <v>15.0444</v>
       </c>
       <c r="E13" t="n">
-        <v>13.9324</v>
+        <v>14.5729</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4715</v>
+        <v>0.4715999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>1.3621</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.771599999999999</v>
+        <v>-2.7716</v>
       </c>
       <c r="I13" t="n">
-        <v>4.133800000000001</v>
+        <v>4.133799999999999</v>
       </c>
       <c r="J13" t="n">
         <v>14.1928</v>
       </c>
       <c r="K13" t="n">
-        <v>2.115899999999999</v>
+        <v>2.1159</v>
       </c>
       <c r="L13" t="n">
         <v>12.0768</v>
@@ -1456,7 +1456,7 @@
         <v>-4.8877</v>
       </c>
       <c r="O13" t="n">
-        <v>-7.943000000000001</v>
+        <v>-7.943</v>
       </c>
       <c r="P13" t="n">
         <v>9.912100000000001</v>
@@ -1468,13 +1468,13 @@
         <v>16.5203</v>
       </c>
       <c r="S13" t="n">
-        <v>2.9446</v>
+        <v>3.5853</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5066</v>
+        <v>2.147199999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>1.438</v>
+        <v>1.4379</v>
       </c>
       <c r="V13" t="n">
         <v>0.185</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.9831</v>
+        <v>2.635</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8683</v>
+        <v>3.2198</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8852</v>
+        <v>-0.5848</v>
       </c>
       <c r="G14" t="n">
         <v>1.3289</v>
@@ -1546,13 +1546,13 @@
         <v>1.1014</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.5661</v>
+        <v>-0.9143</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8687</v>
+        <v>-0.5172</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6974</v>
+        <v>-0.3971</v>
       </c>
       <c r="V14" t="n">
         <v>1.1189</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1806</v>
+        <v>1.1025</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3535</v>
+        <v>2.1191</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1729</v>
+        <v>-1.0167</v>
       </c>
       <c r="G15" t="n">
         <v>-0.0822</v>
@@ -1624,13 +1624,13 @@
         <v>1.3216</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2484</v>
+        <v>-0.3265</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2327</v>
+        <v>-0.0016</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4811</v>
+        <v>-0.3249</v>
       </c>
       <c r="V15" t="n">
         <v>0.1895</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1095</v>
+        <v>0.8872</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4761</v>
+        <v>0.2417</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6334</v>
+        <v>0.6455</v>
       </c>
       <c r="G16" t="n">
         <v>0.7769</v>
@@ -1702,13 +1702,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4445</v>
+        <v>0.2222</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2046</v>
+        <v>-0.0297</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2399</v>
+        <v>0.252</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1119</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. COULIBALY</t>
+          <t>Y. JOSEPH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3595</v>
+        <v>0.4778</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7563</v>
+        <v>2.9545</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3968</v>
+        <v>-2.4767</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5427</v>
+        <v>4.1709</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8585</v>
+        <v>0.2847</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3158</v>
+        <v>3.8862</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2386</v>
+        <v>6.3993</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5931</v>
+        <v>0.7466</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6455</v>
+        <v>5.6527</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6959</v>
+        <v>-2.2283</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2654</v>
+        <v>-0.4619</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9613</v>
+        <v>-1.7665</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2203</v>
+        <v>-2.2027</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.3041</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2203</v>
+        <v>1.1014</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8274</v>
+        <v>-0.746</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3327</v>
+        <v>-0.1407</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4947</v>
+        <v>-0.6052999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2308</v>
+        <v>-0.7444</v>
       </c>
       <c r="W17" t="n">
-        <v>0.185</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.4158</v>
+        <v>-0.7444</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Y. JOSEPH</t>
+          <t>B. COULIBALY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0352</v>
+        <v>0.2071</v>
       </c>
       <c r="E18" t="n">
-        <v>3.0716</v>
+        <v>1.522</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.0364</v>
+        <v>-1.3149</v>
       </c>
       <c r="G18" t="n">
-        <v>4.1709</v>
+        <v>0.5427</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2847</v>
+        <v>0.8585</v>
       </c>
       <c r="I18" t="n">
-        <v>3.8862</v>
+        <v>-0.3158</v>
       </c>
       <c r="J18" t="n">
-        <v>6.3993</v>
+        <v>1.2386</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7466</v>
+        <v>0.5931</v>
       </c>
       <c r="L18" t="n">
-        <v>5.6527</v>
+        <v>0.6455</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.2283</v>
+        <v>-0.6959</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4619</v>
+        <v>0.2654</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.7665</v>
+        <v>-0.9613</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.2027</v>
+        <v>0.2203</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.3041</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1014</v>
+        <v>0.2203</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1886</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0235</v>
+        <v>0.0984</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.165</v>
+        <v>0.5765</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.7444</v>
+        <v>-1.2308</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.185</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.7444</v>
+        <v>-1.4158</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1097</v>
+        <v>-0.8363</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6065</v>
+        <v>0.7236</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7162</v>
+        <v>-1.56</v>
       </c>
       <c r="G19" t="n">
         <v>-1.0176</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0922</v>
+        <v>0.1812</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2562</v>
+        <v>-0.1391</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1641</v>
+        <v>0.3203</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4276</v>
+        <v>-1.4834</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6818</v>
+        <v>-1.5647</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2542</v>
+        <v>0.0813</v>
       </c>
       <c r="G20" t="n">
         <v>1.4434</v>
@@ -2014,13 +2014,13 @@
         <v>0.4405</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0075</v>
+        <v>-0.06320000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3843</v>
+        <v>-0.2672</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3769</v>
+        <v>0.2039</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.794</v>
+        <v>-1.5271</v>
       </c>
       <c r="E21" t="n">
         <v>-0.8742</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9198</v>
+        <v>-0.6529</v>
       </c>
       <c r="G21" t="n">
         <v>-2.2057</v>
@@ -2092,13 +2092,13 @@
         <v>0.8811</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3751</v>
+        <v>-0.1082</v>
       </c>
       <c r="T21" t="n">
         <v>-0.0876</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2875</v>
+        <v>-0.0206</v>
       </c>
       <c r="V21" t="n">
         <v>1.007</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9253</v>
+        <v>-1.7728</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2346</v>
+        <v>-0.4689</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6907</v>
+        <v>-1.3039</v>
       </c>
       <c r="G22" t="n">
         <v>0.3538</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2381</v>
+        <v>0.3905</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3968</v>
+        <v>0.1624</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1587</v>
+        <v>0.2281</v>
       </c>
       <c r="V22" t="n">
         <v>-1.4158</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.9349</v>
+        <v>-3.0437</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.9418</v>
+        <v>-2.2933</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9931</v>
+        <v>-0.7504</v>
       </c>
       <c r="G23" t="n">
         <v>-1.9521</v>
@@ -2248,13 +2248,13 @@
         <v>0.2203</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4622</v>
+        <v>0.3534</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3968</v>
+        <v>0.0453</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0655</v>
+        <v>0.3082</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5639</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.3667</v>
+        <v>-3.6163</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.082</v>
+        <v>-2.7305</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2847</v>
+        <v>-0.8858</v>
       </c>
       <c r="G24" t="n">
         <v>-3.0084</v>
@@ -2326,13 +2326,13 @@
         <v>0.2203</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3829</v>
+        <v>0.3675</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4484</v>
+        <v>-0.0969</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0655</v>
+        <v>0.4644</v>
       </c>
       <c r="V24" t="n">
         <v>1.007</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.5136</v>
+        <v>-5.0905</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.7895</v>
+        <v>-3.3208</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.7241</v>
+        <v>-1.7697</v>
       </c>
       <c r="G25" t="n">
         <v>-1.7129</v>
@@ -2404,13 +2404,13 @@
         <v>1.1014</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.0561</v>
+        <v>-0.633</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9327</v>
+        <v>-0.4641</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1234</v>
+        <v>-0.169</v>
       </c>
       <c r="V25" t="n">
         <v>0.5595</v>
@@ -2437,22 +2437,22 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-14.4039</v>
+        <v>-12.0605</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.4716</v>
+        <v>-0.4717000000000011</v>
       </c>
       <c r="F26" t="n">
-        <v>-13.9323</v>
+        <v>-11.589</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.3623</v>
+        <v>-1.362300000000001</v>
       </c>
       <c r="H26" t="n">
         <v>2.7716</v>
       </c>
       <c r="I26" t="n">
-        <v>-4.1339</v>
+        <v>-4.133900000000001</v>
       </c>
       <c r="J26" t="n">
         <v>12.8308</v>
@@ -2482,13 +2482,13 @@
         <v>6.6083</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.944700000000001</v>
+        <v>-0.6015</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.4378</v>
+        <v>-1.438</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.5065</v>
+        <v>0.8365</v>
       </c>
       <c r="V26" t="n">
         <v>-0.1849</v>
@@ -2497,7 +2497,7 @@
         <v>4.6562</v>
       </c>
       <c r="X26" t="n">
-        <v>-4.841200000000001</v>
+        <v>-4.8412</v>
       </c>
     </row>
   </sheetData>
